--- a/PersonalFindings.xlsx
+++ b/PersonalFindings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kasim\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\CCG_Interns\Engineering_Labs\TrainingProgram\Dotnet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAC8088-60F3-4F6E-BF28-B257B9CE53EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425879C6-CD8C-475C-AA1D-5871244EC592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0C8D8F9B-FC17-4023-98C0-CF651D2841DB}"/>
   </bookViews>
@@ -16,6 +16,11 @@
     <sheet name="Comparisons" sheetId="1" r:id="rId1"/>
     <sheet name="ISO" sheetId="2" r:id="rId2"/>
     <sheet name="Interns Daily" sheetId="3" r:id="rId3"/>
+    <sheet name="GitLab CE" sheetId="4" r:id="rId4"/>
+    <sheet name="IdP" sheetId="5" r:id="rId5"/>
+    <sheet name="Aknts" sheetId="6" r:id="rId6"/>
+    <sheet name="HelpDesk" sheetId="7" r:id="rId7"/>
+    <sheet name="Documentation" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="208">
   <si>
     <t>Shared library</t>
   </si>
@@ -282,9 +287,6 @@
   </si>
   <si>
     <t>Open Source Products</t>
-  </si>
-  <si>
-    <t>ubuntu/fedora</t>
   </si>
   <si>
     <t>Authentik</t>
@@ -490,58 +492,282 @@
     <t>Resources</t>
   </si>
   <si>
-    <t>1.https://learn.microsoft.com/en-us/dotnet/csharp/tour-of-csharp/
+    <t>https://youtu.be/YrtFtdTTfv0?si=WwOjKsyCV-Qxo_bU</t>
+  </si>
+  <si>
+    <t>28th July, 26</t>
+  </si>
+  <si>
+    <t>29th July, 26</t>
+  </si>
+  <si>
+    <t>30th July, 26</t>
+  </si>
+  <si>
+    <t>31st July, 26</t>
+  </si>
+  <si>
+    <t>32nd July, 26</t>
+  </si>
+  <si>
+    <t>33rd July, 26</t>
+  </si>
+  <si>
+    <t>34th July, 26</t>
+  </si>
+  <si>
+    <t>35th July, 26</t>
+  </si>
+  <si>
+    <t>36th July, 26</t>
+  </si>
+  <si>
+    <t>1. Get status Assignment, Course</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>GitLab CE</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Source Code
+Management</t>
+  </si>
+  <si>
+    <t>Continuous
+Integration</t>
+  </si>
+  <si>
+    <t>Artifact Registry</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Continuous
+Delivery</t>
+  </si>
+  <si>
+    <t>Observability</t>
+  </si>
+  <si>
+    <t>Doc</t>
+  </si>
+  <si>
+    <t>Jira</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>Jenkins</t>
+  </si>
+  <si>
+    <t>Jfrog</t>
+  </si>
+  <si>
+    <t>Snyk</t>
+  </si>
+  <si>
+    <t>Harness</t>
+  </si>
+  <si>
+    <t>GUI</t>
+  </si>
+  <si>
+    <t>Explorer</t>
+  </si>
+  <si>
+    <t>GNOME/KDE</t>
+  </si>
+  <si>
+    <t>Finder</t>
+  </si>
+  <si>
+    <t>File System</t>
+  </si>
+  <si>
+    <t>NTFS, ReFS</t>
+  </si>
+  <si>
+    <t>ext4, XFS</t>
+  </si>
+  <si>
+    <t>APFS</t>
+  </si>
+  <si>
+    <t>Process Viewer</t>
+  </si>
+  <si>
+    <t>Task Manager</t>
+  </si>
+  <si>
+    <t>ps, top, htop</t>
+  </si>
+  <si>
+    <t>Activity Monitor, top</t>
+  </si>
+  <si>
+    <t>Service Manger</t>
+  </si>
+  <si>
+    <t>Windows Services</t>
+  </si>
+  <si>
+    <t>systemd</t>
+  </si>
+  <si>
+    <t>launchd</t>
+  </si>
+  <si>
+    <t>Boot Loader</t>
+  </si>
+  <si>
+    <t>Windows Boot Loader</t>
+  </si>
+  <si>
+    <t>GRUB</t>
+  </si>
+  <si>
+    <t>Boot.efi</t>
+  </si>
+  <si>
+    <t>Scheduler</t>
+  </si>
+  <si>
+    <t>Task Scheduler</t>
+  </si>
+  <si>
+    <t>Cron</t>
+  </si>
+  <si>
+    <t>lanuched jobs</t>
+  </si>
+  <si>
+    <t>System Logs</t>
+  </si>
+  <si>
+    <t>Event Viewer</t>
+  </si>
+  <si>
+    <t>syslog</t>
+  </si>
+  <si>
+    <t>Console.app</t>
+  </si>
+  <si>
+    <t>Standard Library</t>
+  </si>
+  <si>
+    <t>Win32 API</t>
+  </si>
+  <si>
+    <t>POSIX Standard base C library</t>
+  </si>
+  <si>
+    <t>Paid Subscriptions</t>
+  </si>
+  <si>
+    <t>AWS IAM Identity Centre</t>
+  </si>
+  <si>
+    <t>Entra ID</t>
+  </si>
+  <si>
+    <t>Auth0</t>
+  </si>
+  <si>
+    <t>Ubuntu</t>
+  </si>
+  <si>
+    <t>Fedora</t>
+  </si>
+  <si>
+    <t>Windows Server</t>
+  </si>
+  <si>
+    <t>Red Hat Linux</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
+    <t>GitHub Enterprise</t>
+  </si>
+  <si>
+    <t>BitBucket</t>
+  </si>
+  <si>
+    <t>ErNext</t>
+  </si>
+  <si>
+    <t>HRMS</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.https://learn.microsoft.com/en-us/dotnet/csharp/tour-of-csharp/
 2.https://essentialcsharp.com/home
-3.</t>
-  </si>
-  <si>
-    <t>https://youtu.be/YrtFtdTTfv0?si=WwOjKsyCV-Qxo_bU</t>
-  </si>
-  <si>
-    <t>28th July, 26</t>
-  </si>
-  <si>
-    <t>29th July, 26</t>
-  </si>
-  <si>
-    <t>30th July, 26</t>
-  </si>
-  <si>
-    <t>31st July, 26</t>
-  </si>
-  <si>
-    <t>32nd July, 26</t>
-  </si>
-  <si>
-    <t>33rd July, 26</t>
-  </si>
-  <si>
-    <t>34th July, 26</t>
-  </si>
-  <si>
-    <t>35th July, 26</t>
-  </si>
-  <si>
-    <t>36th July, 26</t>
-  </si>
-  <si>
-    <t>1. Get status Assignment, Course</t>
-  </si>
-  <si>
-    <t>1. Provide them MSN doc &amp; discuss conventions by QnA short session
+Tony Edwards - MAUI dev
+Gerald Versluis
+Anton Martyniuk
+Kanaiya Katarmal
+Stefan Dokic
+Saineshwar Bageri
+Kanaihya Kumar
+Utkranti Patil
+Jakub Florkowski, mBank Warszwa
+3. </t>
+  </si>
+  <si>
+    <t>1. Provide them MSN doc
 2. Provide DotNet resources, LinkedIn connections list
-3. Provide them overview of Internship plan
-4. Discuss with interns about log book &amp; its format assignment, course, question, learnings/tasks. Ask if they need Office Form
-5. Check database they worked
-6. Discuss Course output - Questions format
-7. Get status Assignment, Course in Form</t>
+3. Discuss conventions by QnA short session
+4. Provide them overview of Internship plan
+5. Discuss with interns about log book &amp; its format assignment, course, question, learnings/tasks. Ask if they need Office Form
+6. Check database they worked
+7. Discuss Course output - Questions format
+8. Get status Assignment, Course in Form
+9. Discuss Console 
+10. If assignment not done, discuss AI &amp; give correct understanding</t>
+  </si>
+  <si>
+    <t>PoW</t>
+  </si>
+  <si>
+    <t>Nesan A3 https://github.com/nesdan40/EmployeePayrollApp.git, 
+Megha A1 https://github.com/MeghaScaria/ElectricityBillEstimator, 
+Hanna A2 https://github.com/hannavarughese/LoanEMIPreview/tree/master</t>
+  </si>
+  <si>
+    <t>1. Provided
+2. Provided
+3. Discussed the significance
+4. Provided, shared draw.io ss
+5. Discussed the format. Received template from department &amp; requested to complete internship journal. Shared interns forms for daily status.
+6. MySQL they worked majorly.
+7. Informed them to keep separate chatGpt chat, asked them to share question they
+8. All of them completed Assignment 1,2,3 as assigned. Shown code, shared github URLs for their respective repos.
+9. Planned for Wed 29th July, 26
+10. Discussed how to leverage AI, what difficulties they will face, copy-pasting risk. Waiting for few more assignments to be done, to explain more detailed scenarios</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,16 +805,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -611,16 +862,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -644,7 +955,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -662,6 +972,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="21"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="21"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -669,6 +1024,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFCCFF99"/>
+      <color rgb="FFCCCCFF"/>
+      <color rgb="FF99FF33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -997,296 +1360,407 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6AF47A-3676-4A06-9D82-9BB411BE6FE8}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="27" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D16" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B26" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1294,598 +1768,854 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB38A5B7-E24F-45F4-B5ED-3156BE3FF45E}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" customWidth="1"/>
     <col min="2" max="2" width="68.42578125" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="C1" s="22"/>
+    </row>
+    <row r="2" spans="1:3" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="28"/>
+      <c r="B4" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C8" s="26"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="30"/>
+      <c r="B9" s="26" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
+      <c r="C9" s="26"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="C10" s="24"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="C11" s="25"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C12" s="26" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="24"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="32"/>
+      <c r="B15" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="25"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="33"/>
+      <c r="B16" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="25"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C17" s="26" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="30"/>
+      <c r="B18" s="26" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
+      <c r="C18" s="26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="24" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="C19" s="24"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="28"/>
+      <c r="B20" s="24" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
+      <c r="C20" s="24"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="C21" s="25"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="C22" s="26"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="26" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3" t="s">
+      <c r="C23" s="26"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="24" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="C24" s="24"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="28"/>
+      <c r="B25" s="24" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3" t="s">
+      <c r="C25" s="24"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="25" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="26" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="C27" s="26"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="30"/>
+      <c r="B28" s="26" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3" t="s">
+      <c r="C28" s="26"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="24" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="C29" s="24"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="25" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="C30" s="25"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="32"/>
+      <c r="B31" s="25" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+      <c r="C31" s="25"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
+      <c r="B32" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6E6FB9-B63E-44AC-BEC7-CBC4D95DE55C}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="37.28515625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="5" customWidth="1"/>
+    <col min="2" max="3" width="37.28515625" style="15" customWidth="1"/>
+    <col min="4" max="5" width="11.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="18" t="s">
+      <c r="B6" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" ht="225" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="6"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="6"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{CBFC7FC1-30EF-4C4D-AF50-7EFFEE55EFC9}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{CBFC7FC1-30EF-4C4D-AF50-7EFFEE55EFC9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1FA681-8469-45A7-B018-16A748D0B3DC}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2E539-5A49-45C7-BF58-C415CB67E2BF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB32621-5418-4996-A885-031705E884F4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EAD5C6-1934-4CB7-97FD-A6103817CCB6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ABFA64-CCAE-4B35-B17B-8D06C0D1C15D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PersonalFindings.xlsx
+++ b/PersonalFindings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\CCG_Interns\Engineering_Labs\TrainingProgram\Dotnet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425879C6-CD8C-475C-AA1D-5871244EC592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6793A9-2A94-4417-8636-D5C71C74D0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0C8D8F9B-FC17-4023-98C0-CF651D2841DB}"/>
   </bookViews>
@@ -522,9 +522,6 @@
     <t>36th July, 26</t>
   </si>
   <si>
-    <t>1. Get status Assignment, Course</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -761,6 +758,13 @@
 8. All of them completed Assignment 1,2,3 as assigned. Shown code, shared github URLs for their respective repos.
 9. Planned for Wed 29th July, 26
 10. Discussed how to leverage AI, what difficulties they will face, copy-pasting risk. Waiting for few more assignments to be done, to explain more detailed scenarios</t>
+  </si>
+  <si>
+    <t>1. Get status Assignment, Course
+2. Get Form filled for daily status
+3. Get questions
+4. Discuss new assignment
+5. If completed, provide new assignment</t>
   </si>
 </sst>
 </file>
@@ -1417,111 +1421,111 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="19" t="s">
         <v>187</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>188</v>
       </c>
       <c r="D12" s="20"/>
     </row>
@@ -1793,7 +1797,7 @@
         <v>78</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1801,19 +1805,19 @@
         <v>61</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1824,7 +1828,7 @@
         <v>79</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1833,14 +1837,14 @@
         <v>80</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="25"/>
       <c r="C7" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1885,7 +1889,7 @@
         <v>86</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1928,7 +1932,7 @@
         <v>87</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1937,7 +1941,7 @@
         <v>89</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2050,20 +2054,20 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
       <c r="B32" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C32" s="25"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
@@ -2185,7 +2189,7 @@
         <v>116</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>128</v>
@@ -2262,25 +2266,25 @@
         <v>110</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>139</v>
+      <c r="B7" s="14" t="s">
+        <v>207</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="3"/>
@@ -2506,71 +2510,71 @@
   <sheetData>
     <row r="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2612,7 +2616,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/PersonalFindings.xlsx
+++ b/PersonalFindings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\CCG_Interns\Engineering_Labs\TrainingProgram\Dotnet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6793A9-2A94-4417-8636-D5C71C74D0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BB1D07-6AD7-4142-B949-18D0E5397B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0C8D8F9B-FC17-4023-98C0-CF651D2841DB}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="221">
   <si>
     <t>Shared library</t>
   </si>
@@ -418,15 +418,7 @@
     <t>23rd July, 26</t>
   </si>
   <si>
-    <t>1. Provide interns C# course.
-2. Ask them to complete 3 hours of it.</t>
-  </si>
-  <si>
     <t>22nd July, 26</t>
-  </si>
-  <si>
-    <t>1. Complete Git, GitHub activity
-2. Overview of .NET, hands on in VS2026</t>
   </si>
   <si>
     <t>Status</t>
@@ -446,14 +438,6 @@
 3. Done</t>
   </si>
   <si>
-    <t>1. Freecodecamp course was used
-2. Agreed and worked actively</t>
-  </si>
-  <si>
-    <t>1. Changed git creds to their personal email
-2. Breif exposure of .NET, OOP, VS2026 was given in office</t>
-  </si>
-  <si>
     <t>1. Before afternoon they completed 3 hours of course
 2. Provided assignment
 3. Provided the course</t>
@@ -463,22 +447,6 @@
   </si>
   <si>
     <t>24th July, 26</t>
-  </si>
-  <si>
-    <t>1. Brainstorm assignment with draw.io
-2. Review the assignment, if not done, set it for Monday 27th, Jul,26
-3. Listen their new learnings
-4. Get questions from them
-5. Commit projects to GitHub
-6. Provide them coding guidelines MSN</t>
-  </si>
-  <si>
-    <t>1. Brainstorm Hana's assignment.
-2. Megha &amp; Jesan didn't started. Configured git &amp; github for their projects
-3. They progressed in course
-4. Megha asked solution view vs folder view
-5. Committed all of them. Megah progressed assignment by creating Model class, Servcie class &amp; Menu code
-6. Couldn't provide because time exceeded.</t>
   </si>
   <si>
     <t>1. Done
@@ -728,6 +696,34 @@
 3. </t>
   </si>
   <si>
+    <t>PoW</t>
+  </si>
+  <si>
+    <t>Nesan A3 https://github.com/nesdan40/EmployeePayrollApp.git, 
+Megha A1 https://github.com/MeghaScaria/ElectricityBillEstimator, 
+Hanna A2 https://github.com/hannavarughese/LoanEMIPreview/tree/master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Done
+2. Done
+3. Done
+4. Done
+5. Done
+6. Done
+7. Done
+8. Done
+9. Pending
+10. Done </t>
+  </si>
+  <si>
+    <t>1. Attendance
+2. Get status Assignment, Course
+3. Get Form filled for daily status
+4. Get questions
+5. Discuss new assignment
+6. If completed, provide new assignment</t>
+  </si>
+  <si>
     <t>1. Provide them MSN doc
 2. Provide DotNet resources, LinkedIn connections list
 3. Discuss conventions by QnA short session
@@ -737,15 +733,8 @@
 7. Discuss Course output - Questions format
 8. Get status Assignment, Course in Form
 9. Discuss Console 
-10. If assignment not done, discuss AI &amp; give correct understanding</t>
-  </si>
-  <si>
-    <t>PoW</t>
-  </si>
-  <si>
-    <t>Nesan A3 https://github.com/nesdan40/EmployeePayrollApp.git, 
-Megha A1 https://github.com/MeghaScaria/ElectricityBillEstimator, 
-Hanna A2 https://github.com/hannavarughese/LoanEMIPreview/tree/master</t>
+10. If assignment not done, discuss AI &amp; give correct understanding
+11. Attendance</t>
   </si>
   <si>
     <t>1. Provided
@@ -757,14 +746,125 @@
 7. Informed them to keep separate chatGpt chat, asked them to share question they
 8. All of them completed Assignment 1,2,3 as assigned. Shown code, shared github URLs for their respective repos.
 9. Planned for Wed 29th July, 26
-10. Discussed how to leverage AI, what difficulties they will face, copy-pasting risk. Waiting for few more assignments to be done, to explain more detailed scenarios</t>
-  </si>
-  <si>
-    <t>1. Get status Assignment, Course
-2. Get Form filled for daily status
-3. Get questions
-4. Discuss new assignment
+10. Discussed how to leverage AI, what difficulties they will face, copy-pasting risk. Waiting for few more assignments to be done, to explain more detailed scenarios
+11. Attendance</t>
+  </si>
+  <si>
+    <t>1. Brainstorm assignment with draw.io
+2. Review the assignment, if not done, set it for Monday 27th, Jul,26
+3. Listen their new learnings
+4. Get questions from them
+5. Commit projects to GitHub
+6. Provide them coding guidelines MSN
+7. Attendance</t>
+  </si>
+  <si>
+    <t>1. Brainstorm Hana's assignment.
+2. Megha &amp; Jesan didn't started. Configured git &amp; github for their projects
+3. They progressed in course
+4. Megha asked solution view vs folder view
+5. Committed all of them. Megah progressed assignment by creating Model class, Servcie class &amp; Menu code
+6. Couldn't provide because time exceeded.
+7. All were present</t>
+  </si>
+  <si>
+    <t>1. Complete Git, GitHub activity
+2. Overview of .NET, hands on in VS2026
+3. Attendance</t>
+  </si>
+  <si>
+    <t>1. Changed git creds to their personal email
+2. Breif exposure of .NET, OOP, VS2026 was given in office
+3. All were present</t>
+  </si>
+  <si>
+    <t>1. Freecodecamp course was used
+2. Agreed and worked actively
+3. All were present</t>
+  </si>
+  <si>
+    <t>1. Provide interns C# course.
+2. Ask them to complete 3 hours of it.
+3. Attendance</t>
+  </si>
+  <si>
+    <t>1. All were present, Hanna's mom was admitted to hospital.
+2. Megha Completed A6, Started CIC002. Hanna 80% completred assignment. Nesan implmented 80% assignment. All 3 created good folder structure for reusage.
+3. Myself filling up for now.
+4. Asked them to enlist and send
+All of them had hands on with CI/CD taught in the course
+5. Provided new assignemnet 7-10
+6. Functionality not tested yet. Will be checked tomorrow Wed 29th July, 26</t>
+  </si>
+  <si>
+    <t>1. Done
+2. Done
+3. Done
+4. InProg
+5. Done
+6. Done</t>
+  </si>
+  <si>
+    <t>1. https://github.com/hannavarughese/PasswordStrengthAnalyzer
+2. https://github.com/hannavarughese/devsecops-crash-course-pygoat
+3. https://github.com/nesdan40/ECommerceEligibilityApp.git
+4. https://github.com/nesdan40/devsecops-crash-course-pygoat.git
+5. https://github.com/MeghaScaria/VehicleTollCalculator
+6. https://github.com/MeghaScaria/devsecops-crash-course-pygoat</t>
+  </si>
+  <si>
+    <t>1. Attendance
+2. Debugging activity
+3. Framework/ A repetitive structure
+4. Extra if any</t>
+  </si>
+  <si>
+    <t>1. All were present in office
+2. Debugging was shown in live coding session
+3. Started working on framework
+4. HR activity was conducted by Ishika</t>
+  </si>
+  <si>
+    <t>1. Done
+2. Done
+3. InProg
+4. Done</t>
+  </si>
+  <si>
+    <t>1. Attendance
+2. Get status Assignment, Course
+3. Get Form filled for daily status
+4. Get questions
 5. If completed, provide new assignment</t>
+  </si>
+  <si>
+    <t>1. https://github.com/nesdan40/IncomeTaxCalculatorApp.git
+2. https://github.com/MeghaScaria/UniversityGradingSystem
+3. https://github.com/hannavarughese/HospitalTriageSystem</t>
+  </si>
+  <si>
+    <t>1. All were present in call
+2. Assignment 7,8,9 was completed
+3. Done
+4. Got questions from Megha, Nesan. Jenny shared plan for tomorrow's session
+5. Today decided to provide them a same assignment so they get to implement OOP, Singleton design pattern. They will be ready for next assignments of db, file handling.</t>
+  </si>
+  <si>
+    <t>1. Done
+2. Done
+3. Done
+4. Done
+5. Done</t>
+  </si>
+  <si>
+    <t>1. Attendance
+2. No assignment was given
+3. Session from Jenny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sign is given. When call will start, will update this
+2. No assignmnet
+3. </t>
   </si>
 </sst>
 </file>
@@ -973,14 +1073,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -988,28 +1094,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="21"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="21"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1020,6 +1114,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="21"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="21"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1374,8 +1474,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1421,113 +1521,113 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="20"/>
+        <v>180</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="24"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -1781,13 +1881,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="22"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1797,280 +1897,280 @@
         <v>78</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>194</v>
+      <c r="B3" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
-      <c r="B4" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>195</v>
+      <c r="B4" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>189</v>
+      <c r="C5" s="19" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="20"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="20"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="18"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="19"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="18"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="19"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="19"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="31"/>
+      <c r="B16" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="19"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="26"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="26"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="24"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="25"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="24"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="25"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
-      <c r="B15" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="25"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>197</v>
-      </c>
-    </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="26" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>198</v>
+      <c r="C18" s="20" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="24"/>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="24"/>
+      <c r="C20" s="18"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="25"/>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="26"/>
+      <c r="C22" s="20"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="26" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="26"/>
+      <c r="C23" s="20"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="24"/>
+      <c r="C24" s="18"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="28"/>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="24"/>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="25"/>
+      <c r="C26" s="19"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="26"/>
+      <c r="C27" s="20"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="26" t="s">
+      <c r="A28" s="26"/>
+      <c r="B28" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="26"/>
+      <c r="C28" s="20"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="24"/>
+      <c r="C29" s="18"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="25"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="32"/>
-      <c r="B31" s="25" t="s">
+      <c r="A31" s="30"/>
+      <c r="B31" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="25"/>
+      <c r="C31" s="19"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="C32" s="25"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="19"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
+      <c r="A33" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
+      <c r="A34" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
@@ -2171,8 +2271,9 @@
   <cols>
     <col min="1" max="1" width="23.28515625" style="1" customWidth="1"/>
     <col min="2" max="3" width="37.28515625" style="15" customWidth="1"/>
-    <col min="4" max="5" width="11.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34" style="1" customWidth="1"/>
+    <col min="6" max="6" width="41.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2183,313 +2284,339 @@
         <v>108</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="B3" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="5"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>119</v>
+      <c r="D4" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="E4" s="9"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" ht="180" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>127</v>
+        <v>204</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="E5" s="9"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" ht="330" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>199</v>
+      </c>
       <c r="E6" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="270" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>214</v>
+      </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="5"/>
+        <v>127</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="5"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="5"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="5"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="3"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="5"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="3"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="5"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="5"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
-      <c r="D21" s="3"/>
+      <c r="D21" s="5"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="5"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="3"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="5"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="3"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="5"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="3"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="5"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="3"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
-      <c r="D26" s="3"/>
+      <c r="D26" s="5"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="5"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
-      <c r="D27" s="3"/>
+      <c r="D27" s="5"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
-      <c r="D28" s="3"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
-      <c r="D29" s="3"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="5"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
-      <c r="D30" s="3"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="5"/>
+      <c r="F30" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2510,71 +2637,71 @@
   <sheetData>
     <row r="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>143</v>
+      <c r="A3" s="16" t="s">
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>144</v>
+      <c r="A4" s="16" t="s">
+        <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>148</v>
+      <c r="A8" s="16" t="s">
+        <v>142</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2616,7 +2743,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/PersonalFindings.xlsx
+++ b/PersonalFindings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\CCG_Interns\Engineering_Labs\TrainingProgram\Dotnet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BB1D07-6AD7-4142-B949-18D0E5397B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4B7337-685B-4895-BD93-1BA98F9B414D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0C8D8F9B-FC17-4023-98C0-CF651D2841DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C8D8F9B-FC17-4023-98C0-CF651D2841DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparisons" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="266">
   <si>
     <t>Shared library</t>
   </si>
@@ -862,9 +862,147 @@
 3. Session from Jenny</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sign is given. When call will start, will update this
+    <t>1. Sign is given. When call will start, will update this
 2. No assignmnet
-3. </t>
+3. Jenny checked their repos which they forked from repo provided in tutorial</t>
+  </si>
+  <si>
+    <t>C#</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>Language Feature</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Static</t>
+  </si>
+  <si>
+    <t>OOP</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>Compiled To</t>
+  </si>
+  <si>
+    <t>MSIL</t>
+  </si>
+  <si>
+    <t>JS</t>
+  </si>
+  <si>
+    <t>CLR</t>
+  </si>
+  <si>
+    <t>WASM</t>
+  </si>
+  <si>
+    <t>Node</t>
+  </si>
+  <si>
+    <t>Deno</t>
+  </si>
+  <si>
+    <t>Browser</t>
+  </si>
+  <si>
+    <t>Project Description File</t>
+  </si>
+  <si>
+    <t>.csproj</t>
+  </si>
+  <si>
+    <t>Common JS</t>
+  </si>
+  <si>
+    <t>Build Folder</t>
+  </si>
+  <si>
+    <t>Debug/Release</t>
+  </si>
+  <si>
+    <t>/build or /dist</t>
+  </si>
+  <si>
+    <t>package.json</t>
+  </si>
+  <si>
+    <t>Compiler Option</t>
+  </si>
+  <si>
+    <t>tsconfig.json</t>
+  </si>
+  <si>
+    <t>Compiler Name</t>
+  </si>
+  <si>
+    <t>Roslyn</t>
+  </si>
+  <si>
+    <t>tsc</t>
+  </si>
+  <si>
+    <t>Run Time Environment</t>
+  </si>
+  <si>
+    <t>.NET Core</t>
+  </si>
+  <si>
+    <t>Execution Engine</t>
+  </si>
+  <si>
+    <t>V8</t>
+  </si>
+  <si>
+    <t>WASM RT</t>
+  </si>
+  <si>
+    <t>Browser(like 
+wasmtime,
+wasmedge )</t>
+  </si>
+  <si>
+    <t>Mono</t>
+  </si>
+  <si>
+    <t>SpiderMonkey</t>
+  </si>
+  <si>
+    <t>Cloudfare Workers</t>
+  </si>
+  <si>
+    <t>React-Native</t>
+  </si>
+  <si>
+    <t>Bun</t>
+  </si>
+  <si>
+    <t>Electron(Renderer 
+as well as Main)</t>
+  </si>
+  <si>
+    <t>Module Standards</t>
+  </si>
+  <si>
+    <t>ES Modules</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>Dependency Distribution</t>
+  </si>
+  <si>
+    <t>NuGet</t>
+  </si>
+  <si>
+    <t>npm</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1172,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1120,6 +1258,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="21"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1464,20 +1617,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6AF47A-3676-4A06-9D82-9BB411BE6FE8}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" style="4" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" style="4" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" style="4" customWidth="1"/>
     <col min="4" max="4" width="27" style="4" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="17" style="4" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
     </row>
-    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>50</v>
       </c>
@@ -1490,8 +1646,17 @@
       <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I2" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -1504,8 +1669,17 @@
       <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I3" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>44</v>
       </c>
@@ -1518,8 +1692,17 @@
       <c r="D4" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I4" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>151</v>
       </c>
@@ -1532,8 +1715,17 @@
       <c r="D5" s="5" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I5" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="K5" s="35" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>155</v>
       </c>
@@ -1546,8 +1738,13 @@
       <c r="D6" s="5" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I6" s="36"/>
+      <c r="J6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="K6" s="36"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>159</v>
       </c>
@@ -1560,8 +1757,17 @@
       <c r="D7" s="5" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I7" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>163</v>
       </c>
@@ -1574,8 +1780,13 @@
       <c r="D8" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>167</v>
       </c>
@@ -1588,8 +1799,13 @@
       <c r="D9" s="5" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I9" s="37"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>175</v>
       </c>
@@ -1602,8 +1818,15 @@
       <c r="D10" s="5" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I10" s="37"/>
+      <c r="J10" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>171</v>
       </c>
@@ -1616,8 +1839,13 @@
       <c r="D11" s="5" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>179</v>
       </c>
@@ -1628,8 +1856,13 @@
         <v>181</v>
       </c>
       <c r="D12" s="24"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>0</v>
       </c>
@@ -1642,8 +1875,13 @@
       <c r="D13" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -1656,8 +1894,13 @@
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
@@ -1670,8 +1913,17 @@
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="I15" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>3</v>
       </c>
@@ -1684,8 +1936,17 @@
       <c r="D16" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I16" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
@@ -1698,8 +1959,17 @@
       <c r="D17" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="I17" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="J17" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1712,8 +1982,13 @@
       <c r="D18" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="I18" s="34"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
@@ -1726,8 +2001,17 @@
       <c r="D19" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I19" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -1740,8 +2024,17 @@
       <c r="D20" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I20" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>33</v>
       </c>
@@ -1754,8 +2047,17 @@
       <c r="D21" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I21" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>54</v>
       </c>
@@ -1768,8 +2070,15 @@
       <c r="D22" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I22" s="37"/>
+      <c r="J22" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>51</v>
       </c>
@@ -1782,8 +2091,13 @@
       <c r="D23" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I23" s="36"/>
+      <c r="J23" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>56</v>
       </c>
@@ -1796,8 +2110,17 @@
       <c r="D24" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I24" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>13</v>
       </c>
@@ -1811,7 +2134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
@@ -1825,46 +2148,54 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="10">
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="I7:I14"/>
+    <mergeCell ref="J10:J14"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="J17:J18"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2434,7 +2765,7 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>127</v>
       </c>

--- a/PersonalFindings.xlsx
+++ b/PersonalFindings.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\CCG_Interns\Engineering_Labs\TrainingProgram\Dotnet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4B7337-685B-4895-BD93-1BA98F9B414D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845E6A46-DA22-46C1-BE8C-CC87EEDB63FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C8D8F9B-FC17-4023-98C0-CF651D2841DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{0C8D8F9B-FC17-4023-98C0-CF651D2841DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparisons" sheetId="1" r:id="rId1"/>
-    <sheet name="ISO" sheetId="2" r:id="rId2"/>
-    <sheet name="Interns Daily" sheetId="3" r:id="rId3"/>
-    <sheet name="GitLab CE" sheetId="4" r:id="rId4"/>
-    <sheet name="IdP" sheetId="5" r:id="rId5"/>
-    <sheet name="Aknts" sheetId="6" r:id="rId6"/>
-    <sheet name="HelpDesk" sheetId="7" r:id="rId7"/>
-    <sheet name="Documentation" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId2"/>
+    <sheet name="ISO" sheetId="2" r:id="rId3"/>
+    <sheet name="Interns Daily" sheetId="3" r:id="rId4"/>
+    <sheet name="GitLab CE" sheetId="4" r:id="rId5"/>
+    <sheet name="IdP" sheetId="5" r:id="rId6"/>
+    <sheet name="Aknts" sheetId="6" r:id="rId7"/>
+    <sheet name="HelpDesk" sheetId="7" r:id="rId8"/>
+    <sheet name="Documentation" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="336">
   <si>
     <t>Shared library</t>
   </si>
@@ -475,21 +476,6 @@
     <t>31st July, 26</t>
   </si>
   <si>
-    <t>32nd July, 26</t>
-  </si>
-  <si>
-    <t>33rd July, 26</t>
-  </si>
-  <si>
-    <t>34th July, 26</t>
-  </si>
-  <si>
-    <t>35th July, 26</t>
-  </si>
-  <si>
-    <t>36th July, 26</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -1003,6 +989,234 @@
   </si>
   <si>
     <t>npm</t>
+  </si>
+  <si>
+    <t>Line_1</t>
+  </si>
+  <si>
+    <t>Line_2</t>
+  </si>
+  <si>
+    <t>Line_3</t>
+  </si>
+  <si>
+    <t>Line_4</t>
+  </si>
+  <si>
+    <t>Line_5</t>
+  </si>
+  <si>
+    <t>Line_6</t>
+  </si>
+  <si>
+    <t>Line_7</t>
+  </si>
+  <si>
+    <t>UnitsProduced1</t>
+  </si>
+  <si>
+    <t>UnitsProduced2</t>
+  </si>
+  <si>
+    <t>UnitsProduced3</t>
+  </si>
+  <si>
+    <t>UnitsProduced4</t>
+  </si>
+  <si>
+    <t>UnitsProduced5</t>
+  </si>
+  <si>
+    <t>UnitsProduced6</t>
+  </si>
+  <si>
+    <t>UnitsProduced7</t>
+  </si>
+  <si>
+    <t>UnitsProduced8</t>
+  </si>
+  <si>
+    <t>UnitsProduced9</t>
+  </si>
+  <si>
+    <t>UnitsProduced10</t>
+  </si>
+  <si>
+    <t>UnitsProduced11</t>
+  </si>
+  <si>
+    <t>UnitsProduced12</t>
+  </si>
+  <si>
+    <t>UnitsProduced13</t>
+  </si>
+  <si>
+    <t>UnitsProduced14</t>
+  </si>
+  <si>
+    <t>UnitsProduced15</t>
+  </si>
+  <si>
+    <t>UnitsProduced16</t>
+  </si>
+  <si>
+    <t>UnitsProduced17</t>
+  </si>
+  <si>
+    <t>UnitsProduced18</t>
+  </si>
+  <si>
+    <t>UnitsProduced19</t>
+  </si>
+  <si>
+    <t>UnitsProduced20</t>
+  </si>
+  <si>
+    <t>UnitsProduced21</t>
+  </si>
+  <si>
+    <t>UnitsProduced22</t>
+  </si>
+  <si>
+    <t>UnitsProduced23</t>
+  </si>
+  <si>
+    <t>UnitsProduced24</t>
+  </si>
+  <si>
+    <t>UnitsProduced25</t>
+  </si>
+  <si>
+    <t>UnitsProduced26</t>
+  </si>
+  <si>
+    <t>UnitsProduced27</t>
+  </si>
+  <si>
+    <t>UnitsProduced28</t>
+  </si>
+  <si>
+    <t>UnitsProduced29</t>
+  </si>
+  <si>
+    <t>UnitsProduced30</t>
+  </si>
+  <si>
+    <t>UnitsProduced31</t>
+  </si>
+  <si>
+    <t>UnitsProduced32</t>
+  </si>
+  <si>
+    <t>UnitsProduced33</t>
+  </si>
+  <si>
+    <t>UnitsProduced34</t>
+  </si>
+  <si>
+    <t>UnitsProduced35</t>
+  </si>
+  <si>
+    <t>UnitsProduced36</t>
+  </si>
+  <si>
+    <t>UnitsProduced37</t>
+  </si>
+  <si>
+    <t>Shift_1</t>
+  </si>
+  <si>
+    <t>Shift_2</t>
+  </si>
+  <si>
+    <t>Shift_3</t>
+  </si>
+  <si>
+    <t>Shift_4</t>
+  </si>
+  <si>
+    <t>Shift_5</t>
+  </si>
+  <si>
+    <t>Shift_6</t>
+  </si>
+  <si>
+    <t>Shift_7</t>
+  </si>
+  <si>
+    <t>Shift_8</t>
+  </si>
+  <si>
+    <t>Shift_9</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>01st Aug, 26</t>
+  </si>
+  <si>
+    <t>2nd Aug, 26</t>
+  </si>
+  <si>
+    <t>3rd Aug, 26</t>
+  </si>
+  <si>
+    <t>4th Aug, 26</t>
+  </si>
+  <si>
+    <t>5th Aug, 26</t>
+  </si>
+  <si>
+    <t>6th Aug, 26</t>
+  </si>
+  <si>
+    <t>7th Aug, 26</t>
+  </si>
+  <si>
+    <t>8th Aug, 26</t>
+  </si>
+  <si>
+    <t>9th Aug, 26</t>
+  </si>
+  <si>
+    <t>10th Aug, 26</t>
+  </si>
+  <si>
+    <t>11th Aug, 26</t>
+  </si>
+  <si>
+    <t>12th Aug, 26</t>
+  </si>
+  <si>
+    <t>13th Aug, 26</t>
+  </si>
+  <si>
+    <t>14th Aug, 26</t>
+  </si>
+  <si>
+    <t>15th Aug, 26</t>
+  </si>
+  <si>
+    <t>Weekend</t>
+  </si>
+  <si>
+    <t>Interns Are In Mid-Sem Exams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create DCLL based assignment
+</t>
+  </si>
+  <si>
+    <t>1. Create MVVM for their console app 
+assignments</t>
+  </si>
+  <si>
+    <t>1. Create OOP session with Hello World 
+program</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1295,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1167,12 +1381,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1262,6 +1487,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1269,10 +1503,28 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1647,13 +1899,13 @@
         <v>7</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1670,13 +1922,13 @@
         <v>14</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1693,173 +1945,173 @@
         <v>47</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>228</v>
+        <v>149</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>223</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>230</v>
+        <v>224</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I6" s="36"/>
+        <v>153</v>
+      </c>
+      <c r="I6" s="39"/>
       <c r="J6" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="K6" s="36"/>
+        <v>227</v>
+      </c>
+      <c r="K6" s="39"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="J7" s="35" t="s">
-        <v>249</v>
+        <v>157</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="J7" s="38" t="s">
+        <v>244</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
+        <v>161</v>
+      </c>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
       <c r="K8" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="I9" s="37"/>
-      <c r="J9" s="36"/>
+        <v>165</v>
+      </c>
+      <c r="I9" s="41"/>
+      <c r="J9" s="39"/>
       <c r="K9" s="12" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38" t="s">
-        <v>253</v>
+        <v>173</v>
+      </c>
+      <c r="I10" s="41"/>
+      <c r="J10" s="42" t="s">
+        <v>248</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
+        <v>169</v>
+      </c>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
       <c r="K11" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D12" s="24"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
       <c r="K12" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1875,10 +2127,10 @@
       <c r="D13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
       <c r="K13" s="5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1894,10 +2146,10 @@
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
       <c r="K14" s="5" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1914,13 +2166,13 @@
         <v>25</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J15" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="K15" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1937,13 +2189,13 @@
         <v>43</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1960,13 +2212,13 @@
         <v>15</v>
       </c>
       <c r="I17" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="J17" s="35" t="s">
-        <v>262</v>
+        <v>255</v>
+      </c>
+      <c r="J17" s="38" t="s">
+        <v>257</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1983,9 +2235,9 @@
         <v>18</v>
       </c>
       <c r="I18" s="34"/>
-      <c r="J18" s="36"/>
+      <c r="J18" s="39"/>
       <c r="K18" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -2002,13 +2254,13 @@
         <v>28</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2025,13 +2277,13 @@
         <v>32</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2047,14 +2299,14 @@
       <c r="D21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="35" t="s">
-        <v>250</v>
+      <c r="I21" s="38" t="s">
+        <v>245</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2070,12 +2322,12 @@
       <c r="D22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="37"/>
+      <c r="I22" s="41"/>
       <c r="J22" s="12" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2091,9 +2343,9 @@
       <c r="D23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="36"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="5" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K23" s="5"/>
     </row>
@@ -2111,13 +2363,13 @@
         <v>55</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -2202,6 +2454,475 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825DED73-3B0A-42E2-9E94-25974294B67E}">
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="9.140625" style="44"/>
+    <col min="4" max="5" width="9.140625" style="2"/>
+    <col min="6" max="6" width="16.140625" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="43"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="43"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="35"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="35"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="35"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="35"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="35"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="35"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="35"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="35"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="35"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="35"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="35"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="35"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="35"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="35"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="35"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="35"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="35"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="35"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="35"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="35"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="35"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="35"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="35"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="43"/>
+      <c r="D34" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="43"/>
+      <c r="D35" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="43"/>
+      <c r="D36" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="43"/>
+      <c r="D37" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="C20:C25"/>
+    <mergeCell ref="B26:B32"/>
+    <mergeCell ref="C26:C32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A26:A32"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB38A5B7-E24F-45F4-B5ED-3156BE3FF45E}">
   <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2228,7 +2949,7 @@
         <v>78</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2236,19 +2957,19 @@
         <v>61</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="18" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2259,7 +2980,7 @@
         <v>79</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2268,14 +2989,14 @@
         <v>80</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="19"/>
       <c r="B7" s="19"/>
       <c r="C7" s="19" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2320,7 +3041,7 @@
         <v>86</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2363,7 +3084,7 @@
         <v>87</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2372,7 +3093,7 @@
         <v>89</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2485,20 +3206,20 @@
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="31"/>
       <c r="B32" s="19" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C32" s="19"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -2595,7 +3316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6E6FB9-B63E-44AC-BEC7-CBC4D95DE55C}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2621,7 +3342,7 @@
         <v>114</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>122</v>
@@ -2632,10 +3353,10 @@
         <v>111</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>115</v>
@@ -2650,10 +3371,10 @@
         <v>113</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>115</v>
@@ -2682,10 +3403,10 @@
         <v>120</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>121</v>
@@ -2698,19 +3419,19 @@
         <v>110</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="270" x14ac:dyDescent="0.25">
@@ -2718,16 +3439,16 @@
         <v>124</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F7" s="3"/>
     </row>
@@ -2736,13 +3457,13 @@
         <v>125</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -2752,16 +3473,16 @@
         <v>126</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -2770,10 +3491,10 @@
         <v>127</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="9"/>
@@ -2781,56 +3502,74 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+        <v>316</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+        <v>318</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>333</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+        <v>319</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>334</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+        <v>320</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>335</v>
+      </c>
       <c r="D15" s="5"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="5"/>
@@ -2838,7 +3577,9 @@
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="5"/>
@@ -2846,7 +3587,9 @@
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="5"/>
@@ -2854,7 +3597,9 @@
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="5"/>
@@ -2862,7 +3607,9 @@
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
+      <c r="A20" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="5"/>
@@ -2870,7 +3617,9 @@
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>326</v>
+      </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="5"/>
@@ -2878,7 +3627,9 @@
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="5"/>
@@ -2886,7 +3637,9 @@
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
+      <c r="A23" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="5"/>
@@ -2894,7 +3647,9 @@
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="5"/>
@@ -2902,7 +3657,9 @@
       <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="5"/>
@@ -2950,6 +3707,10 @@
       <c r="F30" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{CBFC7FC1-30EF-4C4D-AF50-7EFFEE55EFC9}"/>
@@ -2958,7 +3719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1FA681-8469-45A7-B018-16A748D0B3DC}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2968,71 +3729,71 @@
   <sheetData>
     <row r="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3040,7 +3801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F2E539-5A49-45C7-BF58-C415CB67E2BF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3049,7 +3810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB32621-5418-4996-A885-031705E884F4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3058,7 +3819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EAD5C6-1934-4CB7-97FD-A6103817CCB6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3067,14 +3828,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ABFA64-CCAE-4B35-B17B-8D06C0D1C15D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
